--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanNB(NamAnh)_110926.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_AnhTuanNB(NamAnh)_110926.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A9DE49-E677-4C58-BF1C-4B8DBE812976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F3B79D-62BB-4635-A09F-EA11B39664C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>Hà Nội, ngày 11 tháng 09 năm 2026</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Báo giá khách đã đồng ý sửa, công nợ ghi KD</t>
   </si>
 </sst>
 </file>
@@ -392,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -471,13 +477,43 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -534,47 +570,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,98 +960,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="37" t="s">
+      <c r="A1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="40" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="43" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="45"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="46" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="48"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="30"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="61"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="10"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="62" t="s">
+      <c r="J6" s="34" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="55"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="28"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="10"/>
@@ -1057,12 +1060,12 @@
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="56"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="29"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22" t="s">
         <v>1</v>
@@ -1074,12 +1077,12 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="56"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="29"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="23"/>
@@ -1120,7 +1123,9 @@
       <c r="J10" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="26"/>
+      <c r="K10" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -1155,21 +1160,23 @@
         <f>SUM(H11*I11)</f>
         <v>130000</v>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="26" t="s">
+        <v>33</v>
+      </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="51"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
       <c r="J12" s="17">
         <f>SUM(J11:J11)</f>
         <v>130000</v>
@@ -1191,37 +1198,37 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52" t="s">
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
@@ -1279,20 +1286,20 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54" t="s">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
       <c r="K20" s="8"/>
       <c r="AA20" s="2"/>
     </row>
@@ -1357,6 +1364,12 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="13">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
@@ -1364,12 +1377,6 @@
     <mergeCell ref="F14:J14"/>
     <mergeCell ref="F15:J15"/>
     <mergeCell ref="F20:J20"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A5:J5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
